--- a/game45/web.xlsx
+++ b/game45/web.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>domain</t>
   </si>
@@ -48,7 +48,10 @@
     <t>play.xyxgame.top</t>
   </si>
   <si>
-    <t>pink</t>
+    <t>green</t>
+  </si>
+  <si>
+    <t>play.xyxgame.top1</t>
   </si>
   <si>
     <t>paly.sorrel.cloud</t>
@@ -894,7 +897,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -953,13 +956,10 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1387,56 +1387,61 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
+      <c r="A3" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="20"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="play.xyxgame.top" tooltip="http://xyxgame.top"/>
+    <hyperlink ref="A3" r:id="rId1" display="play.xyxgame.top1" tooltip="http://xyxgame.top"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1485,10 +1490,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1499,10 +1504,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1511,20 +1516,20 @@
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="I5" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:10">
@@ -1532,10 +1537,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="9"/>
       <c r="I6" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:10">
@@ -1545,10 +1550,10 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="I7" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1558,10 +1563,10 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="I8" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1571,10 +1576,10 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="I9" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:10">
